--- a/experiments/datasets/oim_3r2t_dataset.xlsx
+++ b/experiments/datasets/oim_3r2t_dataset.xlsx
@@ -3928,30 +3928,30 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>OIM (Kuramoto)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>['{r3}-&gt;t1', '{r1}-&gt;t2']</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="n">
+        <v>9.178699999999999</v>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>67.07899999999999</v>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="E4" s="11" t="n">
+        <v>38.244</v>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="E6" s="11" t="n">
-        <v>28.155</v>
+        <v>18.522</v>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>0.626</v>
+        <v>0.335</v>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>0.3342</v>
+        <v>0.5497</v>
       </c>
     </row>
     <row r="15">
